--- a/exports/trend_1d/KARURVYSYA_full_report.xlsx
+++ b/exports/trend_1d/KARURVYSYA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42086</v>
+        <v>42087</v>
       </c>
       <c r="H2" t="n">
-        <v>81.25</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>79.58683300099999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.67</v>
+        <v>-3</v>
       </c>
       <c r="L2" t="n">
-        <v>2.02</v>
+        <v>3.61</v>
       </c>
       <c r="M2" t="n">
         <v>1.19</v>
       </c>
       <c r="N2" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
         <v>1.61</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.39</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42179</v>
+        <v>42180</v>
       </c>
       <c r="H3" t="n">
-        <v>66.5</v>
+        <v>70.75</v>
       </c>
       <c r="I3" t="n">
         <v>67.26517087964116</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" t="n">
-        <v>16.19</v>
+        <v>10.84</v>
       </c>
       <c r="L3" t="n">
         <v>2.84</v>
@@ -612,7 +647,7 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.37</v>
+        <v>6.39</v>
       </c>
       <c r="O3" t="n">
         <v>-2.34</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.28</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
       <c r="H4" t="n">
-        <v>66.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>66.36988885976227</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.01</v>
+        <v>-6.57</v>
       </c>
       <c r="L4" t="n">
         <v>7.28</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.61</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42332</v>
+        <v>42334</v>
       </c>
       <c r="H5" t="n">
-        <v>61.4</v>
+        <v>62.3</v>
       </c>
       <c r="I5" t="n">
         <v>62.22707091496576</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K5" t="n">
-        <v>7.11</v>
+        <v>5.75</v>
       </c>
       <c r="L5" t="n">
         <v>2.12</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.82</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42382</v>
+        <v>42383</v>
       </c>
       <c r="H6" t="n">
-        <v>69.15000000000001</v>
+        <v>65.55</v>
       </c>
       <c r="I6" t="n">
         <v>65.8273030217222</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>5.22</v>
       </c>
       <c r="L6" t="n">
         <v>1.93</v>
@@ -783,7 +854,7 @@
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.04</v>
+        <v>5.21</v>
       </c>
       <c r="O6" t="n">
         <v>1.47</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>12.64</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42445</v>
+        <v>42446</v>
       </c>
       <c r="H7" t="n">
-        <v>60.45</v>
+        <v>60.65</v>
       </c>
       <c r="I7" t="n">
         <v>60.54985107635945</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K7" t="n">
-        <v>7.78</v>
+        <v>7.48</v>
       </c>
       <c r="L7" t="n">
         <v>6.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="N7" t="n">
         <v>3.14</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.14</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42571</v>
+        <v>42572</v>
       </c>
       <c r="H8" t="n">
-        <v>73.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>70.97705750387991</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K8" t="n">
-        <v>21.02</v>
+        <v>16.9</v>
       </c>
       <c r="L8" t="n">
         <v>2.56</v>
@@ -897,7 +992,7 @@
         <v>1.23</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>3.41</v>
       </c>
       <c r="O8" t="n">
         <v>0.33</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42664</v>
+        <v>42667</v>
       </c>
       <c r="H9" t="n">
-        <v>70.3</v>
+        <v>70.55</v>
       </c>
       <c r="I9" t="n">
         <v>70.35127658745519</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K9" t="n">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="L9" t="n">
         <v>4.51</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42678</v>
+        <v>42681</v>
       </c>
       <c r="H10" t="n">
-        <v>66.34999999999999</v>
+        <v>66.05</v>
       </c>
       <c r="I10" t="n">
         <v>66.12091154195984</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.95</v>
+        <v>-6.38</v>
       </c>
       <c r="L10" t="n">
         <v>6.95</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42767</v>
+        <v>42768</v>
       </c>
       <c r="H11" t="n">
-        <v>60.35</v>
+        <v>61.5</v>
       </c>
       <c r="I11" t="n">
         <v>60.63702728878746</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" t="n">
-        <v>8.630000000000001</v>
+        <v>6.89</v>
       </c>
       <c r="L11" t="n">
         <v>1.51</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.39</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42933</v>
+        <v>42934</v>
       </c>
       <c r="H12" t="n">
-        <v>97</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>95.61115371772009</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K12" t="n">
-        <v>57.72</v>
+        <v>54.23</v>
       </c>
       <c r="L12" t="n">
         <v>2.28</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.59</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42978</v>
+        <v>42979</v>
       </c>
       <c r="H13" t="n">
-        <v>100.4</v>
+        <v>103.8</v>
       </c>
       <c r="I13" t="n">
         <v>102.5470722065376</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.85</v>
+        <v>-9.44</v>
       </c>
       <c r="L13" t="n">
         <v>10.49</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.26</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43005</v>
+        <v>43006</v>
       </c>
       <c r="H14" t="n">
-        <v>101.25</v>
+        <v>100.85</v>
       </c>
       <c r="I14" t="n">
         <v>100.9214027843041</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.46</v>
+        <v>-2.84</v>
       </c>
       <c r="L14" t="n">
         <v>7.51</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>13.02</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43089</v>
+        <v>43090</v>
       </c>
       <c r="H15" t="n">
-        <v>92.55</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>93.34526078890508</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>8.23</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
         <v>4.41</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>10.36</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H16" t="n">
-        <v>89.40000000000001</v>
+        <v>87.05</v>
       </c>
       <c r="I16" t="n">
         <v>87.64283007548848</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.5</v>
+        <v>-7.98</v>
       </c>
       <c r="L16" t="n">
-        <v>6.55</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>0.43</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>15.95</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43208</v>
+        <v>43209</v>
       </c>
       <c r="H17" t="n">
-        <v>80.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I17" t="n">
         <v>81.16653431093795</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K17" t="n">
-        <v>7.64</v>
+        <v>6.72</v>
       </c>
       <c r="L17" t="n">
         <v>8.5</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>8.48</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43229</v>
+        <v>43230</v>
       </c>
       <c r="H18" t="n">
-        <v>78.65000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="I18" t="n">
         <v>75.92683467071926</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.14</v>
+        <v>-6.71</v>
       </c>
       <c r="L18" t="n">
-        <v>4.93</v>
+        <v>8.74</v>
       </c>
       <c r="M18" t="n">
         <v>0.74</v>
       </c>
       <c r="N18" t="n">
-        <v>3.09</v>
+        <v>3.69</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.39</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43250</v>
+        <v>43251</v>
       </c>
       <c r="H19" t="n">
-        <v>78.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>78.96591055849038</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.89</v>
+        <v>-5.08</v>
       </c>
       <c r="L19" t="n">
-        <v>4.82</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M19" t="n">
         <v>0.92</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43299</v>
+        <v>43300</v>
       </c>
       <c r="H20" t="n">
-        <v>75.2</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>74.94834846526038</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K20" t="n">
-        <v>-5.53</v>
+        <v>-6.6</v>
       </c>
       <c r="L20" t="n">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="M20" t="n">
         <v>1.27</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43312</v>
+        <v>43313</v>
       </c>
       <c r="H21" t="n">
-        <v>75.8</v>
+        <v>81</v>
       </c>
       <c r="I21" t="n">
         <v>80.31492925933041</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.95</v>
+        <v>-8.94</v>
       </c>
       <c r="L21" t="n">
-        <v>4.03</v>
+        <v>11.9</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>6.86</v>
       </c>
       <c r="O21" t="n">
         <v>-1.13</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>11.31</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H22" t="n">
-        <v>76.90000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>75.50451402401883</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>-5.06</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>7.41</v>
+        <v>9.07</v>
       </c>
       <c r="M22" t="n">
         <v>0.76</v>
       </c>
       <c r="N22" t="n">
-        <v>1.72</v>
+        <v>3.58</v>
       </c>
       <c r="O22" t="n">
         <v>6.86</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.54</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43447</v>
+        <v>43448</v>
       </c>
       <c r="H23" t="n">
-        <v>68.2</v>
+        <v>69.7</v>
       </c>
       <c r="I23" t="n">
         <v>68.81989044869843</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="n">
-        <v>8.02</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>4.38</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43494</v>
+        <v>43495</v>
       </c>
       <c r="H24" t="n">
-        <v>74.7</v>
+        <v>72.45</v>
       </c>
       <c r="I24" t="n">
         <v>72.97197304729687</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K24" t="n">
-        <v>7.17</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
         <v>3.66</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.82</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43559</v>
+        <v>43560</v>
       </c>
       <c r="H25" t="n">
-        <v>61</v>
+        <v>64.05</v>
       </c>
       <c r="I25" t="n">
         <v>63.01663689414816</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" t="n">
-        <v>15.8</v>
+        <v>11.59</v>
       </c>
       <c r="L25" t="n">
         <v>3.73</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>11.26</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43630</v>
+        <v>43633</v>
       </c>
       <c r="H26" t="n">
-        <v>62.35</v>
+        <v>61.45</v>
       </c>
       <c r="I26" t="n">
         <v>61.4698226920986</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.65</v>
+        <v>-4.06</v>
       </c>
       <c r="L26" t="n">
-        <v>5.39</v>
+        <v>5.54</v>
       </c>
       <c r="M26" t="n">
         <v>1</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.02</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43797</v>
+        <v>43798</v>
       </c>
       <c r="H27" t="n">
-        <v>49.6</v>
+        <v>52.6</v>
       </c>
       <c r="I27" t="n">
         <v>50.86498213487211</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K27" t="n">
-        <v>19.28</v>
+        <v>14.4</v>
       </c>
       <c r="L27" t="n">
         <v>1.46</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>7</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>11.35</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43837</v>
+        <v>43838</v>
       </c>
       <c r="H28" t="n">
-        <v>47.05</v>
+        <v>46.1</v>
       </c>
       <c r="I28" t="n">
         <v>46.72046224406367</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>-10.55</v>
+        <v>-12.36</v>
       </c>
       <c r="L28" t="n">
-        <v>11.03</v>
+        <v>12.55</v>
       </c>
       <c r="M28" t="n">
         <v>3.82</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.36</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43945</v>
+        <v>43948</v>
       </c>
       <c r="H29" t="n">
-        <v>22.55</v>
+        <v>23.6</v>
       </c>
       <c r="I29" t="n">
         <v>23.47098097190606</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K29" t="n">
-        <v>51.08</v>
+        <v>48.81</v>
       </c>
       <c r="L29" t="n">
         <v>5.42</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>20.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43964</v>
+        <v>43965</v>
       </c>
       <c r="H30" t="n">
-        <v>20.4</v>
+        <v>19.55</v>
       </c>
       <c r="I30" t="n">
         <v>20.33333883012743</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K30" t="n">
-        <v>-13.56</v>
+        <v>-17.16</v>
       </c>
       <c r="L30" t="n">
-        <v>15.89</v>
+        <v>17.8</v>
       </c>
       <c r="M30" t="n">
         <v>1.02</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>24.13</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43986</v>
+        <v>43987</v>
       </c>
       <c r="H31" t="n">
-        <v>20.9</v>
+        <v>22.3</v>
       </c>
       <c r="I31" t="n">
         <v>22.16555251771319</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.91</v>
+        <v>-14.07</v>
       </c>
       <c r="L31" t="n">
         <v>15.09</v>
@@ -2208,7 +2579,7 @@
         <v>4.9</v>
       </c>
       <c r="N31" t="n">
-        <v>4.89</v>
+        <v>6.7</v>
       </c>
       <c r="O31" t="n">
         <v>-4.17</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>18.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H32" t="n">
-        <v>29.85</v>
+        <v>27.8</v>
       </c>
       <c r="I32" t="n">
         <v>29.3856375506982</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K32" t="n">
-        <v>33.86</v>
+        <v>24.66</v>
       </c>
       <c r="L32" t="n">
         <v>7.4</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>18.16</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44140</v>
+        <v>44141</v>
       </c>
       <c r="H33" t="n">
-        <v>27.6</v>
+        <v>28.35</v>
       </c>
       <c r="I33" t="n">
         <v>27.92076516378097</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K33" t="n">
-        <v>0.72</v>
+        <v>-1.98</v>
       </c>
       <c r="L33" t="n">
         <v>7.91</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44224</v>
+        <v>44225</v>
       </c>
       <c r="H34" t="n">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
       <c r="I34" t="n">
         <v>35.4789321186913</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K34" t="n">
-        <v>26.63</v>
+        <v>24.87</v>
       </c>
       <c r="L34" t="n">
         <v>2.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.3</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44231</v>
+        <v>44232</v>
       </c>
       <c r="H35" t="n">
-        <v>40.55</v>
+        <v>44.2</v>
       </c>
       <c r="I35" t="n">
         <v>40.81630600645487</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>-14.55</v>
+        <v>-24.86</v>
       </c>
       <c r="L35" t="n">
-        <v>16.1</v>
+        <v>28.11</v>
       </c>
       <c r="M35" t="n">
         <v>0.97</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>17.69</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H36" t="n">
-        <v>47.3</v>
+        <v>45.4</v>
       </c>
       <c r="I36" t="n">
         <v>45.59515260152281</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="n">
-        <v>7.01</v>
+        <v>2.71</v>
       </c>
       <c r="L36" t="n">
         <v>7.58</v>
@@ -2493,7 +2924,7 @@
         <v>1.48</v>
       </c>
       <c r="N36" t="n">
-        <v>3.81</v>
+        <v>4.02</v>
       </c>
       <c r="O36" t="n">
         <v>9</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>16.39</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H37" t="n">
-        <v>47.8</v>
+        <v>49.4</v>
       </c>
       <c r="I37" t="n">
         <v>49.23182980066964</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.29</v>
+        <v>-8.81</v>
       </c>
       <c r="L37" t="n">
-        <v>11.56</v>
+        <v>12</v>
       </c>
       <c r="M37" t="n">
         <v>2.04</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>11.83</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44362</v>
+        <v>44363</v>
       </c>
       <c r="H38" t="n">
-        <v>44.05</v>
+        <v>43.5</v>
       </c>
       <c r="I38" t="n">
         <v>43.55377275399173</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K38" t="n">
-        <v>-10.83</v>
+        <v>-11.94</v>
       </c>
       <c r="L38" t="n">
-        <v>11.13</v>
+        <v>12.04</v>
       </c>
       <c r="M38" t="n">
         <v>-0</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>11.08</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44454</v>
+        <v>44455</v>
       </c>
       <c r="H39" t="n">
-        <v>36.9</v>
+        <v>38.05</v>
       </c>
       <c r="I39" t="n">
         <v>37.62830949882165</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K39" t="n">
-        <v>15.17</v>
+        <v>12.53</v>
       </c>
       <c r="L39" t="n">
         <v>3.79</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.06</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H40" t="n">
-        <v>44</v>
+        <v>42.2</v>
       </c>
       <c r="I40" t="n">
         <v>42.79053484537039</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K40" t="n">
-        <v>15.64</v>
+        <v>10.91</v>
       </c>
       <c r="L40" t="n">
         <v>3.02</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>20.11</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44573</v>
+        <v>44574</v>
       </c>
       <c r="H41" t="n">
-        <v>40</v>
+        <v>41.85</v>
       </c>
       <c r="I41" t="n">
         <v>41.5963666214857</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K41" t="n">
-        <v>5.21</v>
+        <v>0.83</v>
       </c>
       <c r="L41" t="n">
         <v>6.99</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.49</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H42" t="n">
-        <v>40.2</v>
+        <v>38.55</v>
       </c>
       <c r="I42" t="n">
         <v>38.7078445776528</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.94</v>
+        <v>-7.89</v>
       </c>
       <c r="L42" t="n">
-        <v>5.02</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M42" t="n">
         <v>1.32</v>
       </c>
       <c r="N42" t="n">
-        <v>3.86</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>4.63</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>14.33</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H43" t="n">
-        <v>42.8</v>
+        <v>46.35</v>
       </c>
       <c r="I43" t="n">
         <v>43.19322279480762</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.02</v>
+        <v>-20.23</v>
       </c>
       <c r="L43" t="n">
-        <v>15.43</v>
+        <v>22.31</v>
       </c>
       <c r="M43" t="n">
         <v>1.79</v>
       </c>
       <c r="N43" t="n">
-        <v>3.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="O43" t="n">
         <v>-4.1</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>16.84</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44613</v>
+        <v>44614</v>
       </c>
       <c r="H44" t="n">
-        <v>42</v>
+        <v>40.25</v>
       </c>
       <c r="I44" t="n">
         <v>40.2598800271105</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>-9.390000000000001</v>
+        <v>-13.16</v>
       </c>
       <c r="L44" t="n">
-        <v>9.92</v>
+        <v>13.59</v>
       </c>
       <c r="M44" t="n">
         <v>4.61</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>15.56</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44656</v>
+        <v>44657</v>
       </c>
       <c r="H45" t="n">
-        <v>41.8</v>
+        <v>42.7</v>
       </c>
       <c r="I45" t="n">
         <v>42.19612031956992</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.85</v>
+        <v>-6.09</v>
       </c>
       <c r="L45" t="n">
-        <v>4.6</v>
+        <v>6.71</v>
       </c>
       <c r="M45" t="n">
         <v>5.21</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>11.16</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H46" t="n">
-        <v>40.25</v>
+        <v>39.4</v>
       </c>
       <c r="I46" t="n">
         <v>39.6544277241227</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>-5.74</v>
+        <v>-7.73</v>
       </c>
       <c r="L46" t="n">
-        <v>6.79</v>
+        <v>8.31</v>
       </c>
       <c r="M46" t="n">
         <v>1.47</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>13.28</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44713</v>
+        <v>44714</v>
       </c>
       <c r="H47" t="n">
-        <v>38.15</v>
+        <v>41.25</v>
       </c>
       <c r="I47" t="n">
         <v>39.81406182714804</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K47" t="n">
-        <v>3.17</v>
+        <v>-4.7</v>
       </c>
       <c r="L47" t="n">
-        <v>3.81</v>
+        <v>6.09</v>
       </c>
       <c r="M47" t="n">
         <v>3.37</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O47" t="n">
         <v>-2.11</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>15.19</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44978</v>
+        <v>44979</v>
       </c>
       <c r="H48" t="n">
-        <v>83.09999999999999</v>
+        <v>80.55</v>
       </c>
       <c r="I48" t="n">
         <v>82.55267329015466</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K48" t="n">
-        <v>101.45</v>
+        <v>95.27</v>
       </c>
       <c r="L48" t="n">
         <v>13.09</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>182</v>
+        <v>183</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>9</v>
+      </c>
+      <c r="U48" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>11.97</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45062</v>
+        <v>45063</v>
       </c>
       <c r="H49" t="n">
-        <v>81.40000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="I49" t="n">
         <v>84.55723209537554</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.06</v>
+        <v>-8.69</v>
       </c>
       <c r="L49" t="n">
-        <v>9.56</v>
+        <v>11.55</v>
       </c>
       <c r="M49" t="n">
         <v>1.6</v>
       </c>
       <c r="N49" t="n">
-        <v>5.66</v>
+        <v>7.56</v>
       </c>
       <c r="O49" t="n">
         <v>-3.07</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.46</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45155</v>
+        <v>45156</v>
       </c>
       <c r="H50" t="n">
-        <v>99.84999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I50" t="n">
         <v>98.64763048164212</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K50" t="n">
-        <v>14.05</v>
+        <v>11.25</v>
       </c>
       <c r="L50" t="n">
         <v>6.68</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.18</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45175</v>
+        <v>45176</v>
       </c>
       <c r="H51" t="n">
-        <v>107.85</v>
+        <v>108.9</v>
       </c>
       <c r="I51" t="n">
         <v>108.2891419833258</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.73</v>
+        <v>-11.81</v>
       </c>
       <c r="L51" t="n">
         <v>13.35</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.22</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45358</v>
+        <v>45362</v>
       </c>
       <c r="H52" t="n">
-        <v>148.2</v>
+        <v>146</v>
       </c>
       <c r="I52" t="n">
         <v>146.2508431649252</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K52" t="n">
-        <v>36.09</v>
+        <v>34.07</v>
       </c>
       <c r="L52" t="n">
         <v>4.36</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>11.32</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="H53" t="n">
-        <v>158.45</v>
+        <v>162.4</v>
       </c>
       <c r="I53" t="n">
         <v>159.4896822697956</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.529999999999999</v>
+        <v>-11.23</v>
       </c>
       <c r="L53" t="n">
-        <v>11.2</v>
+        <v>15.62</v>
       </c>
       <c r="M53" t="n">
         <v>1.35</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H54" t="n">
-        <v>165.7</v>
+        <v>147.5</v>
       </c>
       <c r="I54" t="n">
         <v>154.2425213515085</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K54" t="n">
-        <v>2.03</v>
+        <v>-9.17</v>
       </c>
       <c r="L54" t="n">
-        <v>7.64</v>
+        <v>15.79</v>
       </c>
       <c r="M54" t="n">
         <v>2.03</v>
       </c>
       <c r="N54" t="n">
-        <v>4.37</v>
+        <v>10.98</v>
       </c>
       <c r="O54" t="n">
         <v>2.49</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>17.22</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45450</v>
+        <v>45453</v>
       </c>
       <c r="H55" t="n">
-        <v>166.7</v>
+        <v>179.25</v>
       </c>
       <c r="I55" t="n">
         <v>172.8958495477495</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-13.02</v>
+        <v>-21.53</v>
       </c>
       <c r="L55" t="n">
-        <v>14.41</v>
+        <v>23.15</v>
       </c>
       <c r="M55" t="n">
         <v>3.02</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>16.32</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H56" t="n">
-        <v>176.6</v>
+        <v>172.55</v>
       </c>
       <c r="I56" t="n">
         <v>172.5920544523337</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.48</v>
+        <v>-3.74</v>
       </c>
       <c r="L56" t="n">
         <v>11.13</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>13.54</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45581</v>
+        <v>45582</v>
       </c>
       <c r="H57" t="n">
-        <v>170.25</v>
+        <v>180.75</v>
       </c>
       <c r="I57" t="n">
         <v>180.0642112247633</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K57" t="n">
-        <v>1.33</v>
+        <v>-4.75</v>
       </c>
       <c r="L57" t="n">
         <v>11.79</v>
@@ -3690,7 +4373,7 @@
         <v>2.02</v>
       </c>
       <c r="N57" t="n">
-        <v>4.6</v>
+        <v>6.17</v>
       </c>
       <c r="O57" t="n">
         <v>-2.29</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>13.73</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H58" t="n">
-        <v>190.4</v>
+        <v>184.1</v>
       </c>
       <c r="I58" t="n">
         <v>184.6938288241112</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K58" t="n">
-        <v>5.34</v>
+        <v>1.85</v>
       </c>
       <c r="L58" t="n">
         <v>7.75</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>11.38</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45679</v>
+        <v>45680</v>
       </c>
       <c r="H59" t="n">
-        <v>186.5</v>
+        <v>194.5</v>
       </c>
       <c r="I59" t="n">
         <v>190.6940737850232</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.3</v>
+        <v>-5.65</v>
       </c>
       <c r="L59" t="n">
-        <v>4.64</v>
+        <v>6.25</v>
       </c>
       <c r="M59" t="n">
         <v>1.51</v>
       </c>
       <c r="N59" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="O59" t="n">
         <v>-3.31</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>13.54</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="H60" t="n">
-        <v>177.8</v>
+        <v>176.25</v>
       </c>
       <c r="I60" t="n">
         <v>177.1078473333545</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K60" t="n">
-        <v>-8.59</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>9.25</v>
+        <v>11.47</v>
       </c>
       <c r="M60" t="n">
         <v>0.9</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="H61" t="n">
-        <v>174.25</v>
+        <v>175.8</v>
       </c>
       <c r="I61" t="n">
         <v>175.6369826800424</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K61" t="n">
-        <v>1.13</v>
+        <v>0.26</v>
       </c>
       <c r="L61" t="n">
-        <v>0.65</v>
+        <v>1.65</v>
       </c>
       <c r="M61" t="n">
         <v>2.28</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.31</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="H62" t="n">
-        <v>214.05</v>
+        <v>209.1</v>
       </c>
       <c r="I62" t="n">
         <v>210.266113644468</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K62" t="n">
-        <v>21.76</v>
+        <v>18.94</v>
       </c>
       <c r="L62" t="n">
         <v>6</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>7</v>
+      </c>
+      <c r="U62" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>10.24</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="H63" t="n">
-        <v>218.57</v>
+        <v>225.11</v>
       </c>
       <c r="I63" t="n">
         <v>221.2743068021505</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.53</v>
+        <v>-7.66</v>
       </c>
       <c r="L63" t="n">
-        <v>5.35</v>
+        <v>9.52</v>
       </c>
       <c r="M63" t="n">
         <v>0.79</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H64" t="n">
-        <v>312.55</v>
+        <v>292.35</v>
       </c>
       <c r="I64" t="n">
         <v>306.9034613284621</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K64" t="n">
-        <v>38.84</v>
+        <v>29.87</v>
       </c>
       <c r="L64" t="n">
         <v>2.72</v>
       </c>
       <c r="M64" t="n">
-        <v>3.43</v>
+        <v>3.66</v>
       </c>
       <c r="N64" t="n">
-        <v>5.09</v>
+        <v>6.46</v>
       </c>
       <c r="O64" t="n">
         <v>2.99</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>13.84</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="H65" t="n">
-        <v>284.8</v>
+        <v>295.75</v>
       </c>
       <c r="I65" t="n">
         <v>292.0423450515241</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K65" t="n">
-        <v>2.58</v>
+        <v>-1.16</v>
       </c>
       <c r="L65" t="n">
         <v>6</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>15.85</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="H66" t="n">
-        <v>283.9</v>
+        <v>280.2</v>
       </c>
       <c r="I66" t="n">
         <v>281.3247385776672</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.01</v>
+        <v>-5.26</v>
       </c>
       <c r="L66" t="n">
         <v>11.75</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>12.38</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="H67" t="n">
-        <v>295.65</v>
+        <v>305.65</v>
       </c>
       <c r="I67" t="n">
         <v>304.7284350212083</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K67" t="n">
-        <v>-5.51</v>
+        <v>-9.08</v>
       </c>
       <c r="L67" t="n">
-        <v>9.869999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="M67" t="n">
         <v>1.63</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>10.68</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H68" t="n">
-        <v>333.8</v>
+        <v>324.45</v>
       </c>
       <c r="I68" t="n">
         <v>328.0019224940402</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K68" t="n">
-        <v>9.210000000000001</v>
+        <v>6.15</v>
       </c>
       <c r="L68" t="n">
         <v>3.11</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>10.09</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="H69" t="n">
-        <v>342.3</v>
+        <v>348.6</v>
       </c>
       <c r="I69" t="n">
         <v>345.9495526952999</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K69" t="n">
-        <v>-5.5</v>
+        <v>-7.44</v>
       </c>
       <c r="L69" t="n">
-        <v>6.7</v>
+        <v>9.83</v>
       </c>
       <c r="M69" t="n">
         <v>1.43</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,14 @@
       <c r="Q70" t="n">
         <v>11</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9392,7 +10239,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.6</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="6">
@@ -9402,7 +10249,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="7">
@@ -9412,7 +10259,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8">
@@ -9422,7 +10269,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9432,7 +10279,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.8</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="10">
@@ -9442,7 +10289,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.4</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="11">
@@ -9452,7 +10299,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -9462,7 +10309,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9472,7 +10319,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.4</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="14">
@@ -9482,7 +10329,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -9492,7 +10339,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.93</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16">
@@ -9502,7 +10349,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.25</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="17">
@@ -9512,7 +10359,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>101.45</v>
+        <v>95.27</v>
       </c>
     </row>
     <row r="18">
@@ -9522,7 +10369,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="19">
@@ -9532,7 +10379,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.95</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="20">
@@ -9542,7 +10389,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.6</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="21">
@@ -9552,7 +10399,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.1</v>
+        <v>28.11</v>
       </c>
     </row>
     <row r="22">
@@ -9562,7 +10409,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -9572,7 +10419,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -9582,7 +10429,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="25">
@@ -9602,7 +10449,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.6</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="27">
@@ -9612,7 +10459,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.79</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="28">
@@ -9622,7 +10469,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
